--- a/web_preview/sample_data/260310B01S02BA/04 17 26_50.27_Shear/Shear_Analysis_Results.xlsx
+++ b/web_preview/sample_data/260310B01S02BA/04 17 26_50.27_Shear/Shear_Analysis_Results.xlsx
@@ -33,10 +33,10 @@
     <t>Analysis Date</t>
   </si>
   <si>
-    <t>260310B01S02BA</t>
-  </si>
-  <si>
-    <t>2026-06-02 15:55:16</t>
+    <t>04 17 26_50.27_Shear</t>
+  </si>
+  <si>
+    <t>2026-06-24 15:42:35</t>
   </si>
 </sst>
 </file>

--- a/web_preview/sample_data/260310B01S02BA/04 17 26_50.27_Shear/Shear_Analysis_Results.xlsx
+++ b/web_preview/sample_data/260310B01S02BA/04 17 26_50.27_Shear/Shear_Analysis_Results.xlsx
@@ -36,7 +36,7 @@
     <t>04 17 26_50.27_Shear</t>
   </si>
   <si>
-    <t>2026-06-24 15:42:35</t>
+    <t>2026-06-24 16:48:47</t>
   </si>
 </sst>
 </file>
